--- a/output/reports/cv_experiment_Ridge_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Ridge_kmeans_regression.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1051614284515381</v>
+        <v>0.1144897937774658</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.07049655914306641</v>
+        <v>0.07332015037536621</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1051614284515381</v>
+        <v>0.1144897937774658</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.07049655914306641</v>
+        <v>0.07332015037536621</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>

--- a/output/reports/cv_experiment_Ridge_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Ridge_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1144897937774658</v>
+        <v>2.232657670974731</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -506,41 +506,6 @@
         <v>4.23403629040481e-09</v>
       </c>
       <c r="I2" t="inlineStr">
-        <is>
-          <t>{'alpha': 1e-05, 'solver': 'auto'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Ridge</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>5</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.07332015037536621</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" t="n">
-        <v>5.839703932729543e-09</v>
-      </c>
-      <c r="H3" t="n">
-        <v>4.23403629040481e-09</v>
-      </c>
-      <c r="I3" t="inlineStr">
         <is>
           <t>{'alpha': 1e-05, 'solver': 'auto'}</t>
         </is>
@@ -557,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,7 +587,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1144897937774658</v>
+        <v>2.232657670974731</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -637,41 +602,6 @@
         <v>4.23403629040481e-09</v>
       </c>
       <c r="I2" t="inlineStr">
-        <is>
-          <t>{'alpha': 1e-05, 'solver': 'auto'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Ridge</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>5</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.07332015037536621</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" t="n">
-        <v>5.839703932729543e-09</v>
-      </c>
-      <c r="H3" t="n">
-        <v>4.23403629040481e-09</v>
-      </c>
-      <c r="I3" t="inlineStr">
         <is>
           <t>{'alpha': 1e-05, 'solver': 'auto'}</t>
         </is>

--- a/output/reports/cv_experiment_Ridge_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Ridge_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,21 +491,56 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.232657670974731</v>
+        <v>0.1536533832550049</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0.9095295397201048</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0.9134071819812636</v>
       </c>
       <c r="G2" t="n">
-        <v>5.839703932729543e-09</v>
+        <v>5.798959174155399</v>
       </c>
       <c r="H2" t="n">
-        <v>4.23403629040481e-09</v>
+        <v>4.192639414719826</v>
       </c>
       <c r="I2" t="inlineStr">
+        <is>
+          <t>{'alpha': 1e-05, 'solver': 'svd'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.274498462677002</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.9087497339209655</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.9134071819812641</v>
+      </c>
+      <c r="G3" t="n">
+        <v>5.79895917415538</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4.192639414719824</v>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>{'alpha': 1e-05, 'solver': 'auto'}</t>
         </is>
@@ -522,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -587,21 +622,56 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.232657670974731</v>
+        <v>0.1536533832550049</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0.9095295397201048</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0.9134071819812636</v>
       </c>
       <c r="G2" t="n">
-        <v>5.839703932729543e-09</v>
+        <v>5.798959174155399</v>
       </c>
       <c r="H2" t="n">
-        <v>4.23403629040481e-09</v>
+        <v>4.192639414719826</v>
       </c>
       <c r="I2" t="inlineStr">
+        <is>
+          <t>{'alpha': 1e-05, 'solver': 'svd'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.274498462677002</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.9087497339209655</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.9134071819812641</v>
+      </c>
+      <c r="G3" t="n">
+        <v>5.79895917415538</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4.192639414719824</v>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>{'alpha': 1e-05, 'solver': 'auto'}</t>
         </is>

--- a/output/reports/cv_experiment_Ridge_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Ridge_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1536533832550049</v>
+        <v>3.41310715675354</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9095295397201048</v>
+        <v>0.3877195595401206</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9134071819812636</v>
+        <v>0.388308481456991</v>
       </c>
       <c r="G2" t="n">
-        <v>5.798959174155399</v>
+        <v>139.174220118836</v>
       </c>
       <c r="H2" t="n">
-        <v>4.192639414719826</v>
+        <v>104.7575690174803</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'alpha': 1e-05, 'solver': 'svd'}</t>
+          <t>{'alpha': 0.01, 'solver': 'auto'}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.274498462677002</v>
+        <v>7.073643922805786</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9087497339209655</v>
+        <v>0.3876196503827011</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9134071819812641</v>
+        <v>0.388308481456991</v>
       </c>
       <c r="G3" t="n">
-        <v>5.79895917415538</v>
+        <v>139.174220118836</v>
       </c>
       <c r="H3" t="n">
-        <v>4.192639414719824</v>
+        <v>104.7575690174803</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'alpha': 1e-05, 'solver': 'auto'}</t>
+          <t>{'alpha': 0.01, 'solver': 'auto'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>11.66348266601562</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.3875104216903328</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.3883084814570342</v>
+      </c>
+      <c r="G4" t="n">
+        <v>139.1742201188311</v>
+      </c>
+      <c r="H4" t="n">
+        <v>104.7575690174663</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'alpha': 0.01, 'solver': 'svd'}</t>
         </is>
       </c>
     </row>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,23 +657,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1536533832550049</v>
+        <v>3.41310715675354</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9095295397201048</v>
+        <v>0.3877195595401206</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9134071819812636</v>
+        <v>0.388308481456991</v>
       </c>
       <c r="G2" t="n">
-        <v>5.798959174155399</v>
+        <v>139.174220118836</v>
       </c>
       <c r="H2" t="n">
-        <v>4.192639414719826</v>
+        <v>104.7575690174803</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'alpha': 1e-05, 'solver': 'svd'}</t>
+          <t>{'alpha': 0.01, 'solver': 'auto'}</t>
         </is>
       </c>
     </row>
@@ -657,23 +692,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.274498462677002</v>
+        <v>7.073643922805786</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9087497339209655</v>
+        <v>0.3876196503827011</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9134071819812641</v>
+        <v>0.388308481456991</v>
       </c>
       <c r="G3" t="n">
-        <v>5.79895917415538</v>
+        <v>139.174220118836</v>
       </c>
       <c r="H3" t="n">
-        <v>4.192639414719824</v>
+        <v>104.7575690174803</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'alpha': 1e-05, 'solver': 'auto'}</t>
+          <t>{'alpha': 0.01, 'solver': 'auto'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>11.66348266601562</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.3875104216903328</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.3883084814570342</v>
+      </c>
+      <c r="G4" t="n">
+        <v>139.1742201188311</v>
+      </c>
+      <c r="H4" t="n">
+        <v>104.7575690174663</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'alpha': 0.01, 'solver': 'svd'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Ridge_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Ridge_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>3.41310715675354</v>
+        <v>0.1468422412872314</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3877195595401206</v>
+        <v>0.9095323921356325</v>
       </c>
       <c r="F2" t="n">
-        <v>0.388308481456991</v>
+        <v>0.913391387078698</v>
       </c>
       <c r="G2" t="n">
-        <v>139.174220118836</v>
+        <v>5.799488027591681</v>
       </c>
       <c r="H2" t="n">
-        <v>104.7575690174803</v>
+        <v>4.192952527344984</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'alpha': 0.01, 'solver': 'auto'}</t>
+          <t>{'alpha': 0.001, 'solver': 'svd'}</t>
         </is>
       </c>
     </row>
@@ -526,58 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>7.073643922805786</v>
+        <v>0.2012887001037598</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3876196503827011</v>
+        <v>0.9087546108334023</v>
       </c>
       <c r="F3" t="n">
-        <v>0.388308481456991</v>
+        <v>0.9133913870786986</v>
       </c>
       <c r="G3" t="n">
-        <v>139.174220118836</v>
+        <v>5.799488027591662</v>
       </c>
       <c r="H3" t="n">
-        <v>104.7575690174803</v>
+        <v>4.192952527344982</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'alpha': 0.01, 'solver': 'auto'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Ridge</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>11.66348266601562</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.3875104216903328</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.3883084814570342</v>
-      </c>
-      <c r="G4" t="n">
-        <v>139.1742201188311</v>
-      </c>
-      <c r="H4" t="n">
-        <v>104.7575690174663</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'alpha': 0.01, 'solver': 'svd'}</t>
+          <t>{'alpha': 0.001, 'solver': 'auto'}</t>
         </is>
       </c>
     </row>
@@ -592,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -657,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>3.41310715675354</v>
+        <v>0.1468422412872314</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3877195595401206</v>
+        <v>0.9095323921356325</v>
       </c>
       <c r="F2" t="n">
-        <v>0.388308481456991</v>
+        <v>0.913391387078698</v>
       </c>
       <c r="G2" t="n">
-        <v>139.174220118836</v>
+        <v>5.799488027591681</v>
       </c>
       <c r="H2" t="n">
-        <v>104.7575690174803</v>
+        <v>4.192952527344984</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'alpha': 0.01, 'solver': 'auto'}</t>
+          <t>{'alpha': 0.001, 'solver': 'svd'}</t>
         </is>
       </c>
     </row>
@@ -692,58 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>7.073643922805786</v>
+        <v>0.2012887001037598</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3876196503827011</v>
+        <v>0.9087546108334023</v>
       </c>
       <c r="F3" t="n">
-        <v>0.388308481456991</v>
+        <v>0.9133913870786986</v>
       </c>
       <c r="G3" t="n">
-        <v>139.174220118836</v>
+        <v>5.799488027591662</v>
       </c>
       <c r="H3" t="n">
-        <v>104.7575690174803</v>
+        <v>4.192952527344982</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'alpha': 0.01, 'solver': 'auto'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Ridge</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>11.66348266601562</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.3875104216903328</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.3883084814570342</v>
-      </c>
-      <c r="G4" t="n">
-        <v>139.1742201188311</v>
-      </c>
-      <c r="H4" t="n">
-        <v>104.7575690174663</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'alpha': 0.01, 'solver': 'svd'}</t>
+          <t>{'alpha': 0.001, 'solver': 'auto'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Ridge_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Ridge_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1468422412872314</v>
+        <v>0.3879308700561523</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9095323921356325</v>
+        <v>0.9095300303393173</v>
       </c>
       <c r="F2" t="n">
-        <v>0.913391387078698</v>
+        <v>0.9134058172821176</v>
       </c>
       <c r="G2" t="n">
-        <v>5.799488027591681</v>
+        <v>5.799004869650901</v>
       </c>
       <c r="H2" t="n">
-        <v>4.192952527344984</v>
+        <v>4.192663653418609</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'alpha': 0.001, 'solver': 'svd'}</t>
+          <t>{'alpha': 0.0001, 'max_iter': 10000, 'solver': 'svd'}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2012887001037598</v>
+        <v>0.7302658557891846</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9087546108334023</v>
+        <v>0.9087503362676245</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9133913870786986</v>
+        <v>0.913405817282118</v>
       </c>
       <c r="G3" t="n">
-        <v>5.799488027591662</v>
+        <v>5.799004869650883</v>
       </c>
       <c r="H3" t="n">
-        <v>4.192952527344982</v>
+        <v>4.192663653418611</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'alpha': 0.001, 'solver': 'auto'}</t>
+          <t>{'alpha': 0.0001, 'max_iter': 10000, 'solver': 'cholesky'}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1468422412872314</v>
+        <v>0.3879308700561523</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9095323921356325</v>
+        <v>0.9095300303393173</v>
       </c>
       <c r="F2" t="n">
-        <v>0.913391387078698</v>
+        <v>0.9134058172821176</v>
       </c>
       <c r="G2" t="n">
-        <v>5.799488027591681</v>
+        <v>5.799004869650901</v>
       </c>
       <c r="H2" t="n">
-        <v>4.192952527344984</v>
+        <v>4.192663653418609</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'alpha': 0.001, 'solver': 'svd'}</t>
+          <t>{'alpha': 0.0001, 'max_iter': 10000, 'solver': 'svd'}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2012887001037598</v>
+        <v>0.7302658557891846</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9087546108334023</v>
+        <v>0.9087503362676245</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9133913870786986</v>
+        <v>0.913405817282118</v>
       </c>
       <c r="G3" t="n">
-        <v>5.799488027591662</v>
+        <v>5.799004869650883</v>
       </c>
       <c r="H3" t="n">
-        <v>4.192952527344982</v>
+        <v>4.192663653418611</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'alpha': 0.001, 'solver': 'auto'}</t>
+          <t>{'alpha': 0.0001, 'max_iter': 10000, 'solver': 'cholesky'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Ridge_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Ridge_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3879308700561523</v>
+        <v>0.05139994621276855</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9095300303393173</v>
+        <v>0.909534101018917</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9134058172821176</v>
+        <v>0.9133644072758389</v>
       </c>
       <c r="G2" t="n">
-        <v>5.799004869650901</v>
+        <v>5.800391268359031</v>
       </c>
       <c r="H2" t="n">
-        <v>4.192663653418609</v>
+        <v>4.193312097150674</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'alpha': 0.0001, 'max_iter': 10000, 'solver': 'svd'}</t>
+          <t>{'alpha': 0.1, 'max_iter': 10000, 'solver': 'cholesky'}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7302658557891846</v>
+        <v>0.06339335441589355</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9087503362676245</v>
+        <v>0.9087605182651135</v>
       </c>
       <c r="F3" t="n">
-        <v>0.913405817282118</v>
+        <v>0.9133644072815305</v>
       </c>
       <c r="G3" t="n">
-        <v>5.799004869650883</v>
+        <v>5.8003912681685</v>
       </c>
       <c r="H3" t="n">
-        <v>4.192663653418611</v>
+        <v>4.193312096705474</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'alpha': 0.0001, 'max_iter': 10000, 'solver': 'cholesky'}</t>
+          <t>{'alpha': 0.1, 'max_iter': 10000, 'solver': 'lsqr'}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3879308700561523</v>
+        <v>0.05139994621276855</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9095300303393173</v>
+        <v>0.909534101018917</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9134058172821176</v>
+        <v>0.9133644072758389</v>
       </c>
       <c r="G2" t="n">
-        <v>5.799004869650901</v>
+        <v>5.800391268359031</v>
       </c>
       <c r="H2" t="n">
-        <v>4.192663653418609</v>
+        <v>4.193312097150674</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'alpha': 0.0001, 'max_iter': 10000, 'solver': 'svd'}</t>
+          <t>{'alpha': 0.1, 'max_iter': 10000, 'solver': 'cholesky'}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7302658557891846</v>
+        <v>0.06339335441589355</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9087503362676245</v>
+        <v>0.9087605182651135</v>
       </c>
       <c r="F3" t="n">
-        <v>0.913405817282118</v>
+        <v>0.9133644072815305</v>
       </c>
       <c r="G3" t="n">
-        <v>5.799004869650883</v>
+        <v>5.8003912681685</v>
       </c>
       <c r="H3" t="n">
-        <v>4.192663653418611</v>
+        <v>4.193312096705474</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'alpha': 0.0001, 'max_iter': 10000, 'solver': 'cholesky'}</t>
+          <t>{'alpha': 0.1, 'max_iter': 10000, 'solver': 'lsqr'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Ridge_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Ridge_kmeans_regression.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05139994621276855</v>
+        <v>0.03731441497802734</v>
       </c>
       <c r="E2" t="n">
         <v>0.909534101018917</v>
@@ -507,7 +507,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'alpha': 0.1, 'max_iter': 10000, 'solver': 'cholesky'}</t>
+          <t>{'solver': 'cholesky', 'max_iter': 10000, 'alpha': 0.1}</t>
         </is>
       </c>
     </row>
@@ -526,10 +526,10 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.06339335441589355</v>
+        <v>0.06124401092529297</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9087605182651135</v>
+        <v>0.9087605182651902</v>
       </c>
       <c r="F3" t="n">
         <v>0.9133644072815305</v>
@@ -542,7 +542,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'alpha': 0.1, 'max_iter': 10000, 'solver': 'lsqr'}</t>
+          <t>{'solver': 'lsqr', 'max_iter': 10000, 'alpha': 0.1}</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05139994621276855</v>
+        <v>0.03731441497802734</v>
       </c>
       <c r="E2" t="n">
         <v>0.909534101018917</v>
@@ -638,7 +638,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'alpha': 0.1, 'max_iter': 10000, 'solver': 'cholesky'}</t>
+          <t>{'solver': 'cholesky', 'max_iter': 10000, 'alpha': 0.1}</t>
         </is>
       </c>
     </row>
@@ -657,10 +657,10 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.06339335441589355</v>
+        <v>0.06124401092529297</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9087605182651135</v>
+        <v>0.9087605182651902</v>
       </c>
       <c r="F3" t="n">
         <v>0.9133644072815305</v>
@@ -673,7 +673,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'alpha': 0.1, 'max_iter': 10000, 'solver': 'lsqr'}</t>
+          <t>{'solver': 'lsqr', 'max_iter': 10000, 'alpha': 0.1}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Ridge_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Ridge_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03731441497802734</v>
+        <v>28.11352252960205</v>
       </c>
       <c r="E2" t="n">
-        <v>0.909534101018917</v>
+        <v>0.3877192325497514</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9133644072758389</v>
+        <v>0.3883092387008059</v>
       </c>
       <c r="G2" t="n">
-        <v>5.800391268359031</v>
+        <v>139.1741339734124</v>
       </c>
       <c r="H2" t="n">
-        <v>4.193312097150674</v>
+        <v>104.7576252565122</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'solver': 'cholesky', 'max_iter': 10000, 'alpha': 0.1}</t>
+          <t>{'solver': 'cholesky', 'max_iter': 10000, 'alpha': 0.01}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.06124401092529297</v>
+        <v>51.8977997303009</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9087605182651902</v>
+        <v>0.3876193930187798</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9133644072815305</v>
+        <v>0.3883092387008058</v>
       </c>
       <c r="G3" t="n">
-        <v>5.8003912681685</v>
+        <v>139.1741339734124</v>
       </c>
       <c r="H3" t="n">
-        <v>4.193312096705474</v>
+        <v>104.7576252565122</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'solver': 'lsqr', 'max_iter': 10000, 'alpha': 0.1}</t>
+          <t>{'solver': 'svd', 'max_iter': 10000, 'alpha': 0.01}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03731441497802734</v>
+        <v>28.11352252960205</v>
       </c>
       <c r="E2" t="n">
-        <v>0.909534101018917</v>
+        <v>0.3877192325497514</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9133644072758389</v>
+        <v>0.3883092387008059</v>
       </c>
       <c r="G2" t="n">
-        <v>5.800391268359031</v>
+        <v>139.1741339734124</v>
       </c>
       <c r="H2" t="n">
-        <v>4.193312097150674</v>
+        <v>104.7576252565122</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'solver': 'cholesky', 'max_iter': 10000, 'alpha': 0.1}</t>
+          <t>{'solver': 'cholesky', 'max_iter': 10000, 'alpha': 0.01}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.06124401092529297</v>
+        <v>51.8977997303009</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9087605182651902</v>
+        <v>0.3876193930187798</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9133644072815305</v>
+        <v>0.3883092387008058</v>
       </c>
       <c r="G3" t="n">
-        <v>5.8003912681685</v>
+        <v>139.1741339734124</v>
       </c>
       <c r="H3" t="n">
-        <v>4.193312096705474</v>
+        <v>104.7576252565122</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'solver': 'lsqr', 'max_iter': 10000, 'alpha': 0.1}</t>
+          <t>{'solver': 'svd', 'max_iter': 10000, 'alpha': 0.01}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Ridge_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Ridge_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>28.11352252960205</v>
+        <v>0.08863043785095215</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3877192325497514</v>
+        <v>0.2756427052041309</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3883092387008059</v>
+        <v>0.2651571125229343</v>
       </c>
       <c r="G2" t="n">
-        <v>139.1741339734124</v>
+        <v>0.7543978232164172</v>
       </c>
       <c r="H2" t="n">
-        <v>104.7576252565122</v>
+        <v>0.5863230154211657</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'solver': 'cholesky', 'max_iter': 10000, 'alpha': 0.01}</t>
+          <t>{'solver': 'saga', 'max_iter': 10000, 'alpha': 1.0}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>51.8977997303009</v>
+        <v>0.1423959732055664</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3876193930187798</v>
+        <v>0.2772285011706008</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3883092387008058</v>
+        <v>0.2651571125229343</v>
       </c>
       <c r="G3" t="n">
-        <v>139.1741339734124</v>
+        <v>0.7543978232164172</v>
       </c>
       <c r="H3" t="n">
-        <v>104.7576252565122</v>
+        <v>0.5863230154211657</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'solver': 'svd', 'max_iter': 10000, 'alpha': 0.01}</t>
+          <t>{'solver': 'saga', 'max_iter': 10000, 'alpha': 1.0}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>28.11352252960205</v>
+        <v>0.08863043785095215</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3877192325497514</v>
+        <v>0.2756427052041309</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3883092387008059</v>
+        <v>0.2651571125229343</v>
       </c>
       <c r="G2" t="n">
-        <v>139.1741339734124</v>
+        <v>0.7543978232164172</v>
       </c>
       <c r="H2" t="n">
-        <v>104.7576252565122</v>
+        <v>0.5863230154211657</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'solver': 'cholesky', 'max_iter': 10000, 'alpha': 0.01}</t>
+          <t>{'solver': 'saga', 'max_iter': 10000, 'alpha': 1.0}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>51.8977997303009</v>
+        <v>0.1423959732055664</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3876193930187798</v>
+        <v>0.2772285011706008</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3883092387008058</v>
+        <v>0.2651571125229343</v>
       </c>
       <c r="G3" t="n">
-        <v>139.1741339734124</v>
+        <v>0.7543978232164172</v>
       </c>
       <c r="H3" t="n">
-        <v>104.7576252565122</v>
+        <v>0.5863230154211657</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'solver': 'svd', 'max_iter': 10000, 'alpha': 0.01}</t>
+          <t>{'solver': 'saga', 'max_iter': 10000, 'alpha': 1.0}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Ridge_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Ridge_kmeans_regression.xlsx
@@ -491,19 +491,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.08863043785095215</v>
+        <v>0.5712189674377441</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2756427052041309</v>
+        <v>0.1631081258955845</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2651571125229343</v>
+        <v>0.1687566366856434</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7543978232164172</v>
+        <v>91.204868609201</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5863230154211657</v>
+        <v>52.61355946207429</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -526,19 +526,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1423959732055664</v>
+        <v>0.7002668380737305</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2772285011706008</v>
+        <v>0.1637077778427174</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2651571125229343</v>
+        <v>0.1687566366856434</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7543978232164172</v>
+        <v>91.204868609201</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5863230154211657</v>
+        <v>52.61355946207429</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -622,19 +622,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.08863043785095215</v>
+        <v>0.5712189674377441</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2756427052041309</v>
+        <v>0.1631081258955845</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2651571125229343</v>
+        <v>0.1687566366856434</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7543978232164172</v>
+        <v>91.204868609201</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5863230154211657</v>
+        <v>52.61355946207429</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -657,19 +657,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1423959732055664</v>
+        <v>0.7002668380737305</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2772285011706008</v>
+        <v>0.1637077778427174</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2651571125229343</v>
+        <v>0.1687566366856434</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7543978232164172</v>
+        <v>91.204868609201</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5863230154211657</v>
+        <v>52.61355946207429</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>

--- a/output/reports/cv_experiment_Ridge_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Ridge_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5712189674377441</v>
+        <v>0.1164255142211914</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1631081258955845</v>
+        <v>0.909534101018917</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1687566366856434</v>
+        <v>0.9133644072758389</v>
       </c>
       <c r="G2" t="n">
-        <v>91.204868609201</v>
+        <v>5.800391268359031</v>
       </c>
       <c r="H2" t="n">
-        <v>52.61355946207429</v>
+        <v>4.193312097150674</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'max_iter': 10000, 'alpha': 1.0}</t>
+          <t>{'solver': 'cholesky', 'max_iter': 10000, 'alpha': 0.1}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7002668380737305</v>
+        <v>0.07103991508483887</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1637077778427174</v>
+        <v>0.9087605182651902</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1687566366856434</v>
+        <v>0.9133644072815305</v>
       </c>
       <c r="G3" t="n">
-        <v>91.204868609201</v>
+        <v>5.8003912681685</v>
       </c>
       <c r="H3" t="n">
-        <v>52.61355946207429</v>
+        <v>4.193312096705474</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'max_iter': 10000, 'alpha': 1.0}</t>
+          <t>{'solver': 'lsqr', 'max_iter': 10000, 'alpha': 0.1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1252851486206055</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.909045741479711</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9128511910101398</v>
+      </c>
+      <c r="G4" t="n">
+        <v>5.817546224259836</v>
+      </c>
+      <c r="H4" t="n">
+        <v>4.201707106444708</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'solver': 'lsqr', 'max_iter': 10000, 'alpha': 1.0}</t>
         </is>
       </c>
     </row>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,23 +657,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5712189674377441</v>
+        <v>0.1164255142211914</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1631081258955845</v>
+        <v>0.909534101018917</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1687566366856434</v>
+        <v>0.9133644072758389</v>
       </c>
       <c r="G2" t="n">
-        <v>91.204868609201</v>
+        <v>5.800391268359031</v>
       </c>
       <c r="H2" t="n">
-        <v>52.61355946207429</v>
+        <v>4.193312097150674</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'max_iter': 10000, 'alpha': 1.0}</t>
+          <t>{'solver': 'cholesky', 'max_iter': 10000, 'alpha': 0.1}</t>
         </is>
       </c>
     </row>
@@ -657,23 +692,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7002668380737305</v>
+        <v>0.07103991508483887</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1637077778427174</v>
+        <v>0.9087605182651902</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1687566366856434</v>
+        <v>0.9133644072815305</v>
       </c>
       <c r="G3" t="n">
-        <v>91.204868609201</v>
+        <v>5.8003912681685</v>
       </c>
       <c r="H3" t="n">
-        <v>52.61355946207429</v>
+        <v>4.193312096705474</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'max_iter': 10000, 'alpha': 1.0}</t>
+          <t>{'solver': 'lsqr', 'max_iter': 10000, 'alpha': 0.1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1252851486206055</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.909045741479711</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9128511910101398</v>
+      </c>
+      <c r="G4" t="n">
+        <v>5.817546224259836</v>
+      </c>
+      <c r="H4" t="n">
+        <v>4.201707106444708</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'solver': 'lsqr', 'max_iter': 10000, 'alpha': 1.0}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Ridge_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Ridge_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1164255142211914</v>
+        <v>3.862469911575317</v>
       </c>
       <c r="E2" t="n">
-        <v>0.909534101018917</v>
+        <v>0.3877192325497514</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9133644072758389</v>
+        <v>0.3883092387008059</v>
       </c>
       <c r="G2" t="n">
-        <v>5.800391268359031</v>
+        <v>139.1741339734124</v>
       </c>
       <c r="H2" t="n">
-        <v>4.193312097150674</v>
+        <v>104.7576252565122</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'solver': 'cholesky', 'max_iter': 10000, 'alpha': 0.1}</t>
+          <t>{'solver': 'cholesky', 'max_iter': 10000, 'alpha': 0.01}</t>
         </is>
       </c>
     </row>
@@ -526,58 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.07103991508483887</v>
+        <v>8.251466751098633</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9087605182651902</v>
+        <v>0.3876193930187798</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9133644072815305</v>
+        <v>0.3883092387008058</v>
       </c>
       <c r="G3" t="n">
-        <v>5.8003912681685</v>
+        <v>139.1741339734124</v>
       </c>
       <c r="H3" t="n">
-        <v>4.193312096705474</v>
+        <v>104.7576252565122</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'solver': 'lsqr', 'max_iter': 10000, 'alpha': 0.1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Ridge</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.1252851486206055</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.909045741479711</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9128511910101398</v>
-      </c>
-      <c r="G4" t="n">
-        <v>5.817546224259836</v>
-      </c>
-      <c r="H4" t="n">
-        <v>4.201707106444708</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'solver': 'lsqr', 'max_iter': 10000, 'alpha': 1.0}</t>
+          <t>{'solver': 'svd', 'max_iter': 10000, 'alpha': 0.01}</t>
         </is>
       </c>
     </row>
@@ -592,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -657,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1164255142211914</v>
+        <v>3.862469911575317</v>
       </c>
       <c r="E2" t="n">
-        <v>0.909534101018917</v>
+        <v>0.3877192325497514</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9133644072758389</v>
+        <v>0.3883092387008059</v>
       </c>
       <c r="G2" t="n">
-        <v>5.800391268359031</v>
+        <v>139.1741339734124</v>
       </c>
       <c r="H2" t="n">
-        <v>4.193312097150674</v>
+        <v>104.7576252565122</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'solver': 'cholesky', 'max_iter': 10000, 'alpha': 0.1}</t>
+          <t>{'solver': 'cholesky', 'max_iter': 10000, 'alpha': 0.01}</t>
         </is>
       </c>
     </row>
@@ -692,58 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.07103991508483887</v>
+        <v>8.251466751098633</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9087605182651902</v>
+        <v>0.3876193930187798</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9133644072815305</v>
+        <v>0.3883092387008058</v>
       </c>
       <c r="G3" t="n">
-        <v>5.8003912681685</v>
+        <v>139.1741339734124</v>
       </c>
       <c r="H3" t="n">
-        <v>4.193312096705474</v>
+        <v>104.7576252565122</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'solver': 'lsqr', 'max_iter': 10000, 'alpha': 0.1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Ridge</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.1252851486206055</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.909045741479711</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9128511910101398</v>
-      </c>
-      <c r="G4" t="n">
-        <v>5.817546224259836</v>
-      </c>
-      <c r="H4" t="n">
-        <v>4.201707106444708</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'solver': 'lsqr', 'max_iter': 10000, 'alpha': 1.0}</t>
+          <t>{'solver': 'svd', 'max_iter': 10000, 'alpha': 0.01}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Ridge_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Ridge_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>3.862469911575317</v>
+        <v>0.4583749771118164</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3877192325497514</v>
+        <v>0.990098309686355</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3883092387008059</v>
+        <v>0.990254957444855</v>
       </c>
       <c r="G2" t="n">
-        <v>139.1741339734124</v>
+        <v>0.9476793014611543</v>
       </c>
       <c r="H2" t="n">
-        <v>104.7576252565122</v>
+        <v>0.7418452222906518</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'solver': 'cholesky', 'max_iter': 10000, 'alpha': 0.01}</t>
+          <t>{'solver': 'svd', 'max_iter': 10000, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>8.251466751098633</v>
+        <v>0.8081331253051758</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3876193930187798</v>
+        <v>0.9900987126467754</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3883092387008058</v>
+        <v>0.9902550153826634</v>
       </c>
       <c r="G3" t="n">
-        <v>139.1741339734124</v>
+        <v>0.9476764843085843</v>
       </c>
       <c r="H3" t="n">
-        <v>104.7576252565122</v>
+        <v>0.7418426994071522</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'solver': 'svd', 'max_iter': 10000, 'alpha': 0.01}</t>
+          <t>{'solver': 'saga', 'max_iter': 10000, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>3.862469911575317</v>
+        <v>0.4583749771118164</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3877192325497514</v>
+        <v>0.990098309686355</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3883092387008059</v>
+        <v>0.990254957444855</v>
       </c>
       <c r="G2" t="n">
-        <v>139.1741339734124</v>
+        <v>0.9476793014611543</v>
       </c>
       <c r="H2" t="n">
-        <v>104.7576252565122</v>
+        <v>0.7418452222906518</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'solver': 'cholesky', 'max_iter': 10000, 'alpha': 0.01}</t>
+          <t>{'solver': 'svd', 'max_iter': 10000, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>8.251466751098633</v>
+        <v>0.8081331253051758</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3876193930187798</v>
+        <v>0.9900987126467754</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3883092387008058</v>
+        <v>0.9902550153826634</v>
       </c>
       <c r="G3" t="n">
-        <v>139.1741339734124</v>
+        <v>0.9476764843085843</v>
       </c>
       <c r="H3" t="n">
-        <v>104.7576252565122</v>
+        <v>0.7418426994071522</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'solver': 'svd', 'max_iter': 10000, 'alpha': 0.01}</t>
+          <t>{'solver': 'saga', 'max_iter': 10000, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Ridge_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Ridge_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4583749771118164</v>
+        <v>0.4936785697937012</v>
       </c>
       <c r="E2" t="n">
-        <v>0.990098309686355</v>
+        <v>0.1631081258955845</v>
       </c>
       <c r="F2" t="n">
-        <v>0.990254957444855</v>
+        <v>0.1687566366856434</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9476793014611543</v>
+        <v>91.204868609201</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7418452222906518</v>
+        <v>52.61355946207429</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'solver': 'svd', 'max_iter': 10000, 'alpha': 0.001}</t>
+          <t>{'solver': 'saga', 'max_iter': 10000, 'alpha': 1.0}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8081331253051758</v>
+        <v>0.6994311809539795</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9900987126467754</v>
+        <v>0.1637077778427174</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9902550153826634</v>
+        <v>0.1687566366856434</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9476764843085843</v>
+        <v>91.204868609201</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7418426994071522</v>
+        <v>52.61355946207429</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'max_iter': 10000, 'alpha': 0.001}</t>
+          <t>{'solver': 'saga', 'max_iter': 10000, 'alpha': 1.0}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4583749771118164</v>
+        <v>0.4936785697937012</v>
       </c>
       <c r="E2" t="n">
-        <v>0.990098309686355</v>
+        <v>0.1631081258955845</v>
       </c>
       <c r="F2" t="n">
-        <v>0.990254957444855</v>
+        <v>0.1687566366856434</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9476793014611543</v>
+        <v>91.204868609201</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7418452222906518</v>
+        <v>52.61355946207429</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'solver': 'svd', 'max_iter': 10000, 'alpha': 0.001}</t>
+          <t>{'solver': 'saga', 'max_iter': 10000, 'alpha': 1.0}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8081331253051758</v>
+        <v>0.6994311809539795</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9900987126467754</v>
+        <v>0.1637077778427174</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9902550153826634</v>
+        <v>0.1687566366856434</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9476764843085843</v>
+        <v>91.204868609201</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7418426994071522</v>
+        <v>52.61355946207429</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'max_iter': 10000, 'alpha': 0.001}</t>
+          <t>{'solver': 'saga', 'max_iter': 10000, 'alpha': 1.0}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Ridge_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Ridge_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4936785697937012</v>
+        <v>23.55539107322693</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1631081258955845</v>
+        <v>0.733920064339284</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1687566366856434</v>
+        <v>0.7375098266344251</v>
       </c>
       <c r="G2" t="n">
-        <v>91.204868609201</v>
+        <v>17.38238498910604</v>
       </c>
       <c r="H2" t="n">
-        <v>52.61355946207429</v>
+        <v>13.21099620560328</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'max_iter': 10000, 'alpha': 1.0}</t>
+          <t>{'solver': 'svd', 'max_iter': 10000, 'alpha': 0.1}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6994311809539795</v>
+        <v>51.92563271522522</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1637077778427174</v>
+        <v>0.7339708525065632</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1687566366856434</v>
+        <v>0.7375098266344251</v>
       </c>
       <c r="G3" t="n">
-        <v>91.204868609201</v>
+        <v>17.38238498910604</v>
       </c>
       <c r="H3" t="n">
-        <v>52.61355946207429</v>
+        <v>13.21099620560328</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'max_iter': 10000, 'alpha': 1.0}</t>
+          <t>{'solver': 'svd', 'max_iter': 10000, 'alpha': 0.1}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4936785697937012</v>
+        <v>23.55539107322693</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1631081258955845</v>
+        <v>0.733920064339284</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1687566366856434</v>
+        <v>0.7375098266344251</v>
       </c>
       <c r="G2" t="n">
-        <v>91.204868609201</v>
+        <v>17.38238498910604</v>
       </c>
       <c r="H2" t="n">
-        <v>52.61355946207429</v>
+        <v>13.21099620560328</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'max_iter': 10000, 'alpha': 1.0}</t>
+          <t>{'solver': 'svd', 'max_iter': 10000, 'alpha': 0.1}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6994311809539795</v>
+        <v>51.92563271522522</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1637077778427174</v>
+        <v>0.7339708525065632</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1687566366856434</v>
+        <v>0.7375098266344251</v>
       </c>
       <c r="G3" t="n">
-        <v>91.204868609201</v>
+        <v>17.38238498910604</v>
       </c>
       <c r="H3" t="n">
-        <v>52.61355946207429</v>
+        <v>13.21099620560328</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'max_iter': 10000, 'alpha': 1.0}</t>
+          <t>{'solver': 'svd', 'max_iter': 10000, 'alpha': 0.1}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Ridge_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Ridge_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>23.55539107322693</v>
+        <v>0.103060245513916</v>
       </c>
       <c r="E2" t="n">
-        <v>0.733920064339284</v>
+        <v>0.2756427052041309</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7375098266344251</v>
+        <v>0.2651571125229343</v>
       </c>
       <c r="G2" t="n">
-        <v>17.38238498910604</v>
+        <v>0.7543978232164172</v>
       </c>
       <c r="H2" t="n">
-        <v>13.21099620560328</v>
+        <v>0.5863230154211657</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'solver': 'svd', 'max_iter': 10000, 'alpha': 0.1}</t>
+          <t>{'alpha': 1.0, 'max_iter': 10000, 'solver': 'saga'}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>51.92563271522522</v>
+        <v>0.1919951438903809</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7339708525065632</v>
+        <v>0.2772285011706008</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7375098266344251</v>
+        <v>0.2651571125229343</v>
       </c>
       <c r="G3" t="n">
-        <v>17.38238498910604</v>
+        <v>0.7543978232164172</v>
       </c>
       <c r="H3" t="n">
-        <v>13.21099620560328</v>
+        <v>0.5863230154211657</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'solver': 'svd', 'max_iter': 10000, 'alpha': 0.1}</t>
+          <t>{'alpha': 1.0, 'max_iter': 10000, 'solver': 'saga'}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>23.55539107322693</v>
+        <v>0.103060245513916</v>
       </c>
       <c r="E2" t="n">
-        <v>0.733920064339284</v>
+        <v>0.2756427052041309</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7375098266344251</v>
+        <v>0.2651571125229343</v>
       </c>
       <c r="G2" t="n">
-        <v>17.38238498910604</v>
+        <v>0.7543978232164172</v>
       </c>
       <c r="H2" t="n">
-        <v>13.21099620560328</v>
+        <v>0.5863230154211657</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'solver': 'svd', 'max_iter': 10000, 'alpha': 0.1}</t>
+          <t>{'alpha': 1.0, 'max_iter': 10000, 'solver': 'saga'}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>51.92563271522522</v>
+        <v>0.1919951438903809</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7339708525065632</v>
+        <v>0.2772285011706008</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7375098266344251</v>
+        <v>0.2651571125229343</v>
       </c>
       <c r="G3" t="n">
-        <v>17.38238498910604</v>
+        <v>0.7543978232164172</v>
       </c>
       <c r="H3" t="n">
-        <v>13.21099620560328</v>
+        <v>0.5863230154211657</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'solver': 'svd', 'max_iter': 10000, 'alpha': 0.1}</t>
+          <t>{'alpha': 1.0, 'max_iter': 10000, 'solver': 'saga'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Ridge_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Ridge_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.103060245513916</v>
+        <v>0.08847928047180176</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2756427052041309</v>
+        <v>0.909534101018917</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2651571125229343</v>
+        <v>0.9133644072758389</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7543978232164172</v>
+        <v>5.800391268359031</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5863230154211657</v>
+        <v>4.193312097150674</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'alpha': 1.0, 'max_iter': 10000, 'solver': 'saga'}</t>
+          <t>{'solver': 'cholesky', 'max_iter': 10000, 'alpha': 0.1}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1919951438903809</v>
+        <v>0.07600307464599609</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2772285011706008</v>
+        <v>0.9087605182651902</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2651571125229343</v>
+        <v>0.9133644072815305</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7543978232164172</v>
+        <v>5.8003912681685</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5863230154211657</v>
+        <v>4.193312096705474</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'alpha': 1.0, 'max_iter': 10000, 'solver': 'saga'}</t>
+          <t>{'solver': 'lsqr', 'max_iter': 10000, 'alpha': 0.1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.134225606918335</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.909045741479711</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9128511910101398</v>
+      </c>
+      <c r="G4" t="n">
+        <v>5.817546224259836</v>
+      </c>
+      <c r="H4" t="n">
+        <v>4.201707106444708</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'solver': 'lsqr', 'max_iter': 10000, 'alpha': 1.0}</t>
         </is>
       </c>
     </row>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,23 +657,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.103060245513916</v>
+        <v>0.08847928047180176</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2756427052041309</v>
+        <v>0.909534101018917</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2651571125229343</v>
+        <v>0.9133644072758389</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7543978232164172</v>
+        <v>5.800391268359031</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5863230154211657</v>
+        <v>4.193312097150674</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'alpha': 1.0, 'max_iter': 10000, 'solver': 'saga'}</t>
+          <t>{'solver': 'cholesky', 'max_iter': 10000, 'alpha': 0.1}</t>
         </is>
       </c>
     </row>
@@ -657,23 +692,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1919951438903809</v>
+        <v>0.07600307464599609</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2772285011706008</v>
+        <v>0.9087605182651902</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2651571125229343</v>
+        <v>0.9133644072815305</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7543978232164172</v>
+        <v>5.8003912681685</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5863230154211657</v>
+        <v>4.193312096705474</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'alpha': 1.0, 'max_iter': 10000, 'solver': 'saga'}</t>
+          <t>{'solver': 'lsqr', 'max_iter': 10000, 'alpha': 0.1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.134225606918335</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.909045741479711</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9128511910101398</v>
+      </c>
+      <c r="G4" t="n">
+        <v>5.817546224259836</v>
+      </c>
+      <c r="H4" t="n">
+        <v>4.201707106444708</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'solver': 'lsqr', 'max_iter': 10000, 'alpha': 1.0}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Ridge_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Ridge_kmeans_regression.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.08847928047180176</v>
+        <v>0.07427597045898438</v>
       </c>
       <c r="E2" t="n">
         <v>0.909534101018917</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.07600307464599609</v>
+        <v>0.09237909317016602</v>
       </c>
       <c r="E3" t="n">
         <v>0.9087605182651902</v>
@@ -561,7 +561,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.134225606918335</v>
+        <v>0.138779878616333</v>
       </c>
       <c r="E4" t="n">
         <v>0.909045741479711</v>
@@ -657,7 +657,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.08847928047180176</v>
+        <v>0.07427597045898438</v>
       </c>
       <c r="E2" t="n">
         <v>0.909534101018917</v>
@@ -692,7 +692,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.07600307464599609</v>
+        <v>0.09237909317016602</v>
       </c>
       <c r="E3" t="n">
         <v>0.9087605182651902</v>
@@ -727,7 +727,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.134225606918335</v>
+        <v>0.138779878616333</v>
       </c>
       <c r="E4" t="n">
         <v>0.909045741479711</v>

--- a/output/reports/cv_experiment_Ridge_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Ridge_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,26 +488,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>0.07427597045898438</v>
+        <v>0.4543380737304688</v>
       </c>
       <c r="E2" t="n">
-        <v>0.909534101018917</v>
+        <v>0.3879676979818973</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9133644072758389</v>
+        <v>0.3785530597229144</v>
       </c>
       <c r="G2" t="n">
-        <v>5.800391268359031</v>
+        <v>105.1382440718104</v>
       </c>
       <c r="H2" t="n">
-        <v>4.193312097150674</v>
+        <v>79.46521830767777</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'solver': 'cholesky', 'max_iter': 10000, 'alpha': 0.1}</t>
+          <t>{'solver': 'saga', 'max_iter': 10000, 'alpha': 1.0}</t>
         </is>
       </c>
     </row>
@@ -523,61 +523,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>0.09237909317016602</v>
+        <v>0.677628755569458</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9087605182651902</v>
+        <v>0.3876142441170848</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9133644072815305</v>
+        <v>0.3785530597229144</v>
       </c>
       <c r="G3" t="n">
-        <v>5.8003912681685</v>
+        <v>105.1382440718104</v>
       </c>
       <c r="H3" t="n">
-        <v>4.193312096705474</v>
+        <v>79.46521830767777</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'solver': 'lsqr', 'max_iter': 10000, 'alpha': 0.1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Ridge</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.138779878616333</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.909045741479711</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9128511910101398</v>
-      </c>
-      <c r="G4" t="n">
-        <v>5.817546224259836</v>
-      </c>
-      <c r="H4" t="n">
-        <v>4.201707106444708</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'solver': 'lsqr', 'max_iter': 10000, 'alpha': 1.0}</t>
+          <t>{'solver': 'saga', 'max_iter': 10000, 'alpha': 1.0}</t>
         </is>
       </c>
     </row>
@@ -592,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -654,26 +619,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>0.07427597045898438</v>
+        <v>0.4543380737304688</v>
       </c>
       <c r="E2" t="n">
-        <v>0.909534101018917</v>
+        <v>0.3879676979818973</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9133644072758389</v>
+        <v>0.3785530597229144</v>
       </c>
       <c r="G2" t="n">
-        <v>5.800391268359031</v>
+        <v>105.1382440718104</v>
       </c>
       <c r="H2" t="n">
-        <v>4.193312097150674</v>
+        <v>79.46521830767777</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'solver': 'cholesky', 'max_iter': 10000, 'alpha': 0.1}</t>
+          <t>{'solver': 'saga', 'max_iter': 10000, 'alpha': 1.0}</t>
         </is>
       </c>
     </row>
@@ -689,61 +654,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>0.09237909317016602</v>
+        <v>0.677628755569458</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9087605182651902</v>
+        <v>0.3876142441170848</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9133644072815305</v>
+        <v>0.3785530597229144</v>
       </c>
       <c r="G3" t="n">
-        <v>5.8003912681685</v>
+        <v>105.1382440718104</v>
       </c>
       <c r="H3" t="n">
-        <v>4.193312096705474</v>
+        <v>79.46521830767777</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'solver': 'lsqr', 'max_iter': 10000, 'alpha': 0.1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Ridge</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.138779878616333</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.909045741479711</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9128511910101398</v>
-      </c>
-      <c r="G4" t="n">
-        <v>5.817546224259836</v>
-      </c>
-      <c r="H4" t="n">
-        <v>4.201707106444708</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'solver': 'lsqr', 'max_iter': 10000, 'alpha': 1.0}</t>
+          <t>{'solver': 'saga', 'max_iter': 10000, 'alpha': 1.0}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Ridge_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Ridge_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,26 +488,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4543380737304688</v>
+        <v>0.08175039291381836</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3879676979818973</v>
+        <v>0.909534101018917</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3785530597229144</v>
+        <v>0.9133644072758389</v>
       </c>
       <c r="G2" t="n">
-        <v>105.1382440718104</v>
+        <v>5.800391268359031</v>
       </c>
       <c r="H2" t="n">
-        <v>79.46521830767777</v>
+        <v>4.193312097150674</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'max_iter': 10000, 'alpha': 1.0}</t>
+          <t>{'solver': 'cholesky', 'max_iter': 10000, 'alpha': 0.1}</t>
         </is>
       </c>
     </row>
@@ -523,26 +523,61 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.677628755569458</v>
+        <v>0.1122102737426758</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3876142441170848</v>
+        <v>0.9087605182651902</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3785530597229144</v>
+        <v>0.9133644072815305</v>
       </c>
       <c r="G3" t="n">
-        <v>105.1382440718104</v>
+        <v>5.8003912681685</v>
       </c>
       <c r="H3" t="n">
-        <v>79.46521830767777</v>
+        <v>4.193312096705474</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'max_iter': 10000, 'alpha': 1.0}</t>
+          <t>{'solver': 'lsqr', 'max_iter': 10000, 'alpha': 0.1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.2052247524261475</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.909045741479711</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9128511910101398</v>
+      </c>
+      <c r="G4" t="n">
+        <v>5.817546224259836</v>
+      </c>
+      <c r="H4" t="n">
+        <v>4.201707106444708</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'solver': 'lsqr', 'max_iter': 10000, 'alpha': 1.0}</t>
         </is>
       </c>
     </row>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -619,26 +654,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4543380737304688</v>
+        <v>0.08175039291381836</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3879676979818973</v>
+        <v>0.909534101018917</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3785530597229144</v>
+        <v>0.9133644072758389</v>
       </c>
       <c r="G2" t="n">
-        <v>105.1382440718104</v>
+        <v>5.800391268359031</v>
       </c>
       <c r="H2" t="n">
-        <v>79.46521830767777</v>
+        <v>4.193312097150674</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'max_iter': 10000, 'alpha': 1.0}</t>
+          <t>{'solver': 'cholesky', 'max_iter': 10000, 'alpha': 0.1}</t>
         </is>
       </c>
     </row>
@@ -654,26 +689,61 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.677628755569458</v>
+        <v>0.1122102737426758</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3876142441170848</v>
+        <v>0.9087605182651902</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3785530597229144</v>
+        <v>0.9133644072815305</v>
       </c>
       <c r="G3" t="n">
-        <v>105.1382440718104</v>
+        <v>5.8003912681685</v>
       </c>
       <c r="H3" t="n">
-        <v>79.46521830767777</v>
+        <v>4.193312096705474</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'max_iter': 10000, 'alpha': 1.0}</t>
+          <t>{'solver': 'lsqr', 'max_iter': 10000, 'alpha': 0.1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.2052247524261475</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.909045741479711</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9128511910101398</v>
+      </c>
+      <c r="G4" t="n">
+        <v>5.817546224259836</v>
+      </c>
+      <c r="H4" t="n">
+        <v>4.201707106444708</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'solver': 'lsqr', 'max_iter': 10000, 'alpha': 1.0}</t>
         </is>
       </c>
     </row>
